--- a/04-excel-analysis/average-weekly-cattle-prices-classroom.xlsx
+++ b/04-excel-analysis/average-weekly-cattle-prices-classroom.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E157"/>
+  <dimension ref="A1:E150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,12 +438,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Steer_900_999_Price</t>
+          <t>Steer_900_999_lbs_Price_per_cwt_live</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Steer_1250plus_Price</t>
+          <t>Steer_over_1250_lbs_Price_per_cwt_live</t>
         </is>
       </c>
     </row>
@@ -2978,125 +2978,6 @@
       </c>
       <c r="E150" t="n">
         <v>330.25</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>0</v>
-      </c>
-      <c r="B151" t="n">
-        <v>0</v>
-      </c>
-      <c r="C151" s="1" t="n">
-        <v>46388</v>
-      </c>
-      <c r="D151" t="n">
-        <v>0</v>
-      </c>
-      <c r="E151" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>0</v>
-      </c>
-      <c r="B152" t="n">
-        <v>0</v>
-      </c>
-      <c r="C152" s="1" t="n">
-        <v>46395</v>
-      </c>
-      <c r="D152" t="n">
-        <v>0</v>
-      </c>
-      <c r="E152" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>0</v>
-      </c>
-      <c r="B153" t="n">
-        <v>0</v>
-      </c>
-      <c r="C153" s="1" t="n">
-        <v>46402</v>
-      </c>
-      <c r="D153" t="n">
-        <v>0</v>
-      </c>
-      <c r="E153" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>0</v>
-      </c>
-      <c r="B154" t="n">
-        <v>0</v>
-      </c>
-      <c r="C154" s="1" t="n">
-        <v>46409</v>
-      </c>
-      <c r="D154" t="n">
-        <v>0</v>
-      </c>
-      <c r="E154" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>0</v>
-      </c>
-      <c r="B155" t="n">
-        <v>0</v>
-      </c>
-      <c r="C155" s="1" t="n">
-        <v>46416</v>
-      </c>
-      <c r="D155" t="n">
-        <v>0</v>
-      </c>
-      <c r="E155" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>0</v>
-      </c>
-      <c r="B156" t="n">
-        <v>0</v>
-      </c>
-      <c r="C156" s="1" t="n">
-        <v>46423</v>
-      </c>
-      <c r="D156" t="n">
-        <v>0</v>
-      </c>
-      <c r="E156" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>0</v>
-      </c>
-      <c r="B157" t="n">
-        <v>0</v>
-      </c>
-      <c r="C157" s="1" t="n">
-        <v>46430</v>
-      </c>
-      <c r="D157" t="n">
-        <v>0</v>
-      </c>
-      <c r="E157" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
